--- a/processed_outputs/all_rudder_cases.xlsx
+++ b/processed_outputs/all_rudder_cases.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="84">
   <si>
     <t>run</t>
   </si>
@@ -227,7 +227,10 @@
     <t>source_file</t>
   </si>
   <si>
-    <t>rudder_deg</t>
+    <t>dR</t>
+  </si>
+  <si>
+    <t>dE</t>
   </si>
   <si>
     <t>V_round</t>
@@ -624,10 +627,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BW31"/>
+  <dimension ref="A1:BX31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:75">
+    <row r="1" spans="1:76">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,8 +856,11 @@
       <c r="BW1" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="2" spans="1:75">
+    <row r="2" spans="1:76">
       <c r="A2">
         <v>28</v>
       </c>
@@ -1057,31 +1063,34 @@
         <v>-22.5</v>
       </c>
       <c r="BP2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR2">
         <v>0</v>
       </c>
       <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
         <v>20</v>
       </c>
-      <c r="BT2">
+      <c r="BU2">
         <v>2.5</v>
       </c>
-      <c r="BU2">
+      <c r="BV2">
         <v>-10</v>
       </c>
-      <c r="BV2">
+      <c r="BW2">
         <v>1.9981249644582</v>
       </c>
-      <c r="BW2">
+      <c r="BX2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:75">
+    <row r="3" spans="1:76">
       <c r="A3">
         <v>20</v>
       </c>
@@ -1284,31 +1293,34 @@
         <v>-22.5</v>
       </c>
       <c r="BP3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR3">
         <v>0</v>
       </c>
       <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
         <v>40</v>
       </c>
-      <c r="BT3">
+      <c r="BU3">
         <v>2.5</v>
       </c>
-      <c r="BU3">
+      <c r="BV3">
         <v>-10</v>
       </c>
-      <c r="BV3">
+      <c r="BW3">
         <v>1.999624949296554</v>
       </c>
-      <c r="BW3">
+      <c r="BX3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:75">
+    <row r="4" spans="1:76">
       <c r="A4">
         <v>26</v>
       </c>
@@ -1511,31 +1523,34 @@
         <v>-13.9</v>
       </c>
       <c r="BP4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR4">
         <v>0</v>
       </c>
       <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
         <v>20</v>
       </c>
-      <c r="BT4">
+      <c r="BU4">
         <v>2.5</v>
       </c>
-      <c r="BU4">
+      <c r="BV4">
         <v>-8</v>
       </c>
-      <c r="BV4">
+      <c r="BW4">
         <v>1.998061565906423</v>
       </c>
-      <c r="BW4">
+      <c r="BX4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:75">
+    <row r="5" spans="1:76">
       <c r="A5">
         <v>25</v>
       </c>
@@ -1738,31 +1753,34 @@
         <v>-7.8</v>
       </c>
       <c r="BP5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR5">
         <v>0</v>
       </c>
       <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
         <v>20</v>
       </c>
-      <c r="BT5">
+      <c r="BU5">
         <v>2.5</v>
       </c>
-      <c r="BU5">
+      <c r="BV5">
         <v>-4</v>
       </c>
-      <c r="BV5">
+      <c r="BW5">
         <v>1.999052185353145</v>
       </c>
-      <c r="BW5">
+      <c r="BX5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:75">
+    <row r="6" spans="1:76">
       <c r="A6">
         <v>15</v>
       </c>
@@ -1965,31 +1983,34 @@
         <v>-7.8</v>
       </c>
       <c r="BP6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR6">
         <v>0</v>
       </c>
       <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
         <v>40</v>
       </c>
-      <c r="BT6">
+      <c r="BU6">
         <v>2.5</v>
       </c>
-      <c r="BU6">
+      <c r="BV6">
         <v>-4</v>
       </c>
-      <c r="BV6">
+      <c r="BW6">
         <v>1.999134042244398</v>
       </c>
-      <c r="BW6">
+      <c r="BX6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:75">
+    <row r="7" spans="1:76">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2192,31 +2213,34 @@
         <v>-6.2</v>
       </c>
       <c r="BP7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR7">
         <v>0</v>
       </c>
       <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
         <v>40</v>
       </c>
-      <c r="BT7">
+      <c r="BU7">
         <v>-5</v>
       </c>
-      <c r="BU7">
-        <v>0</v>
-      </c>
       <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
         <v>1.599628523547783</v>
       </c>
-      <c r="BW7">
+      <c r="BX7">
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:75">
+    <row r="8" spans="1:76">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2419,31 +2443,34 @@
         <v>-6.2</v>
       </c>
       <c r="BP8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR8">
         <v>0</v>
       </c>
       <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
         <v>40</v>
       </c>
-      <c r="BT8">
+      <c r="BU8">
         <v>-5</v>
       </c>
-      <c r="BU8">
-        <v>0</v>
-      </c>
       <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
         <v>2.398452479684511</v>
       </c>
-      <c r="BW8">
+      <c r="BX8">
         <v>2.4</v>
       </c>
     </row>
-    <row r="9" spans="1:75">
+    <row r="9" spans="1:76">
       <c r="A9">
         <v>21</v>
       </c>
@@ -2646,31 +2673,34 @@
         <v>3.1</v>
       </c>
       <c r="BP9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR9">
         <v>0</v>
       </c>
       <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
         <v>20</v>
       </c>
-      <c r="BT9">
+      <c r="BU9">
         <v>2.5</v>
       </c>
-      <c r="BU9">
-        <v>0</v>
-      </c>
       <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
         <v>1.600409102342839</v>
       </c>
-      <c r="BW9">
+      <c r="BX9">
         <v>1.6</v>
       </c>
     </row>
-    <row r="10" spans="1:75">
+    <row r="10" spans="1:76">
       <c r="A10">
         <v>22</v>
       </c>
@@ -2873,31 +2903,34 @@
         <v>3.1</v>
       </c>
       <c r="BP10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR10">
         <v>0</v>
       </c>
       <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
         <v>20</v>
       </c>
-      <c r="BT10">
+      <c r="BU10">
         <v>2.5</v>
       </c>
-      <c r="BU10">
-        <v>0</v>
-      </c>
       <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
         <v>2.40006841422405</v>
       </c>
-      <c r="BW10">
+      <c r="BX10">
         <v>2.4</v>
       </c>
     </row>
-    <row r="11" spans="1:75">
+    <row r="11" spans="1:76">
       <c r="A11">
         <v>23</v>
       </c>
@@ -3100,31 +3133,34 @@
         <v>3.1</v>
       </c>
       <c r="BP11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR11">
         <v>0</v>
       </c>
       <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
         <v>20</v>
       </c>
-      <c r="BT11">
+      <c r="BU11">
         <v>2.5</v>
       </c>
-      <c r="BU11">
-        <v>0</v>
-      </c>
       <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
         <v>2.798598214688046</v>
       </c>
-      <c r="BW11">
+      <c r="BX11">
         <v>2.8</v>
       </c>
     </row>
-    <row r="12" spans="1:75">
+    <row r="12" spans="1:76">
       <c r="A12">
         <v>24</v>
       </c>
@@ -3327,31 +3363,34 @@
         <v>3.1</v>
       </c>
       <c r="BP12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR12">
         <v>0</v>
       </c>
       <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
         <v>20</v>
       </c>
-      <c r="BT12">
+      <c r="BU12">
         <v>2.5</v>
       </c>
-      <c r="BU12">
-        <v>0</v>
-      </c>
       <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
         <v>2.000930815102612</v>
       </c>
-      <c r="BW12">
+      <c r="BX12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:75">
+    <row r="13" spans="1:76">
       <c r="A13">
         <v>4</v>
       </c>
@@ -3554,31 +3593,34 @@
         <v>3.1</v>
       </c>
       <c r="BP13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR13">
         <v>0</v>
       </c>
       <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
         <v>40</v>
       </c>
-      <c r="BT13">
+      <c r="BU13">
         <v>2.5</v>
       </c>
-      <c r="BU13">
-        <v>0</v>
-      </c>
       <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
         <v>1.599716975777331</v>
       </c>
-      <c r="BW13">
+      <c r="BX13">
         <v>1.6</v>
       </c>
     </row>
-    <row r="14" spans="1:75">
+    <row r="14" spans="1:76">
       <c r="A14">
         <v>10</v>
       </c>
@@ -3781,31 +3823,34 @@
         <v>3.1</v>
       </c>
       <c r="BP14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR14">
         <v>0</v>
       </c>
       <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
         <v>40</v>
       </c>
-      <c r="BT14">
+      <c r="BU14">
         <v>2.5</v>
       </c>
-      <c r="BU14">
-        <v>0</v>
-      </c>
       <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
         <v>2.400019135102187</v>
       </c>
-      <c r="BW14">
+      <c r="BX14">
         <v>2.4</v>
       </c>
     </row>
-    <row r="15" spans="1:75">
+    <row r="15" spans="1:76">
       <c r="A15">
         <v>11</v>
       </c>
@@ -4008,31 +4053,34 @@
         <v>3.1</v>
       </c>
       <c r="BP15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR15">
         <v>0</v>
       </c>
       <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
         <v>40</v>
       </c>
-      <c r="BT15">
+      <c r="BU15">
         <v>2.5</v>
       </c>
-      <c r="BU15">
-        <v>0</v>
-      </c>
       <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
         <v>2.799343737351262</v>
       </c>
-      <c r="BW15">
+      <c r="BX15">
         <v>2.8</v>
       </c>
     </row>
-    <row r="16" spans="1:75">
+    <row r="16" spans="1:76">
       <c r="A16">
         <v>12</v>
       </c>
@@ -4235,31 +4283,34 @@
         <v>3.1</v>
       </c>
       <c r="BP16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR16">
         <v>0</v>
       </c>
       <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
         <v>40</v>
       </c>
-      <c r="BT16">
+      <c r="BU16">
         <v>2.5</v>
       </c>
-      <c r="BU16">
-        <v>0</v>
-      </c>
       <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
         <v>2.00005296202351</v>
       </c>
-      <c r="BW16">
+      <c r="BX16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:75">
+    <row r="17" spans="1:76">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4462,31 +4513,34 @@
         <v>9.4</v>
       </c>
       <c r="BP17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR17">
         <v>0</v>
       </c>
       <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
         <v>40</v>
       </c>
-      <c r="BT17">
+      <c r="BU17">
         <v>5</v>
       </c>
-      <c r="BU17">
-        <v>0</v>
-      </c>
       <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
         <v>1.599983067669266</v>
       </c>
-      <c r="BW17">
+      <c r="BX17">
         <v>1.6</v>
       </c>
     </row>
-    <row r="18" spans="1:75">
+    <row r="18" spans="1:76">
       <c r="A18">
         <v>9</v>
       </c>
@@ -4689,31 +4743,34 @@
         <v>9.4</v>
       </c>
       <c r="BP18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR18">
         <v>0</v>
       </c>
       <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
         <v>40</v>
       </c>
-      <c r="BT18">
+      <c r="BU18">
         <v>5</v>
       </c>
-      <c r="BU18">
-        <v>0</v>
-      </c>
       <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
         <v>2.399774097228049</v>
       </c>
-      <c r="BW18">
+      <c r="BX18">
         <v>2.4</v>
       </c>
     </row>
-    <row r="19" spans="1:75">
+    <row r="19" spans="1:76">
       <c r="A19">
         <v>3</v>
       </c>
@@ -4916,31 +4973,34 @@
         <v>13.75</v>
       </c>
       <c r="BP19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR19">
         <v>0</v>
       </c>
       <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
         <v>40</v>
       </c>
-      <c r="BT19">
+      <c r="BU19">
         <v>7</v>
       </c>
-      <c r="BU19">
-        <v>0</v>
-      </c>
       <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
         <v>1.599296490435402</v>
       </c>
-      <c r="BW19">
+      <c r="BX19">
         <v>1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:75">
+    <row r="20" spans="1:76">
       <c r="A20">
         <v>6</v>
       </c>
@@ -5143,31 +5203,34 @@
         <v>13.75</v>
       </c>
       <c r="BP20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR20">
         <v>0</v>
       </c>
       <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
         <v>40</v>
       </c>
-      <c r="BT20">
+      <c r="BU20">
         <v>7</v>
       </c>
-      <c r="BU20">
-        <v>0</v>
-      </c>
       <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
         <v>2.400793968982889</v>
       </c>
-      <c r="BW20">
+      <c r="BX20">
         <v>2.4</v>
       </c>
     </row>
-    <row r="21" spans="1:75">
+    <row r="21" spans="1:76">
       <c r="A21">
         <v>5</v>
       </c>
@@ -5370,31 +5433,34 @@
         <v>11.5</v>
       </c>
       <c r="BP21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR21">
         <v>0</v>
       </c>
       <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
         <v>40</v>
       </c>
-      <c r="BT21">
+      <c r="BU21">
         <v>8</v>
       </c>
-      <c r="BU21">
-        <v>0</v>
-      </c>
       <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
         <v>1.59988495034755</v>
       </c>
-      <c r="BW21">
+      <c r="BX21">
         <v>1.6</v>
       </c>
     </row>
-    <row r="22" spans="1:75">
+    <row r="22" spans="1:76">
       <c r="A22">
         <v>8</v>
       </c>
@@ -5597,31 +5663,34 @@
         <v>11.5</v>
       </c>
       <c r="BP22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR22">
         <v>0</v>
       </c>
       <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
         <v>40</v>
       </c>
-      <c r="BT22">
+      <c r="BU22">
         <v>8</v>
       </c>
-      <c r="BU22">
-        <v>0</v>
-      </c>
       <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
         <v>2.400401445800175</v>
       </c>
-      <c r="BW22">
+      <c r="BX22">
         <v>2.4</v>
       </c>
     </row>
-    <row r="23" spans="1:75">
+    <row r="23" spans="1:76">
       <c r="A23">
         <v>13</v>
       </c>
@@ -5824,31 +5893,34 @@
         <v>11.5</v>
       </c>
       <c r="BP23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR23">
         <v>0</v>
       </c>
       <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
         <v>40</v>
       </c>
-      <c r="BT23">
+      <c r="BU23">
         <v>8</v>
       </c>
-      <c r="BU23">
-        <v>0</v>
-      </c>
       <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
         <v>1.999514789764307</v>
       </c>
-      <c r="BW23">
+      <c r="BX23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:75">
+    <row r="24" spans="1:76">
       <c r="A24">
         <v>27</v>
       </c>
@@ -6051,31 +6123,34 @@
         <v>1.6</v>
       </c>
       <c r="BP24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR24">
         <v>0</v>
       </c>
       <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
         <v>20</v>
       </c>
-      <c r="BT24">
+      <c r="BU24">
         <v>2.5</v>
       </c>
-      <c r="BU24">
+      <c r="BV24">
         <v>4</v>
       </c>
-      <c r="BV24">
+      <c r="BW24">
         <v>2.00257726863807</v>
       </c>
-      <c r="BW24">
+      <c r="BX24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:75">
+    <row r="25" spans="1:76">
       <c r="A25">
         <v>16</v>
       </c>
@@ -6278,31 +6353,34 @@
         <v>1.6</v>
       </c>
       <c r="BP25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR25">
         <v>0</v>
       </c>
       <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
         <v>40</v>
       </c>
-      <c r="BT25">
+      <c r="BU25">
         <v>2.5</v>
       </c>
-      <c r="BU25">
+      <c r="BV25">
         <v>4</v>
       </c>
-      <c r="BV25">
+      <c r="BW25">
         <v>1.996844465052762</v>
       </c>
-      <c r="BW25">
+      <c r="BX25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:75">
+    <row r="26" spans="1:76">
       <c r="A26">
         <v>17</v>
       </c>
@@ -6505,31 +6583,34 @@
         <v>1.6</v>
       </c>
       <c r="BP26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR26">
         <v>0</v>
       </c>
       <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
         <v>40</v>
       </c>
-      <c r="BT26">
+      <c r="BU26">
         <v>2.5</v>
       </c>
-      <c r="BU26">
+      <c r="BV26">
         <v>4</v>
       </c>
-      <c r="BV26">
+      <c r="BW26">
         <v>1.999311380750595</v>
       </c>
-      <c r="BW26">
+      <c r="BX26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:75">
+    <row r="27" spans="1:76">
       <c r="A27">
         <v>29</v>
       </c>
@@ -6732,31 +6813,34 @@
         <v>5.8</v>
       </c>
       <c r="BP27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR27">
         <v>0</v>
       </c>
       <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
         <v>20</v>
       </c>
-      <c r="BT27">
+      <c r="BU27">
         <v>2.5</v>
       </c>
-      <c r="BU27">
+      <c r="BV27">
         <v>8</v>
       </c>
-      <c r="BV27">
+      <c r="BW27">
         <v>2.000608505594573</v>
       </c>
-      <c r="BW27">
+      <c r="BX27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:75">
+    <row r="28" spans="1:76">
       <c r="A28">
         <v>14</v>
       </c>
@@ -6959,31 +7043,34 @@
         <v>5.8</v>
       </c>
       <c r="BP28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR28">
         <v>0</v>
       </c>
       <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
         <v>40</v>
       </c>
-      <c r="BT28">
+      <c r="BU28">
         <v>2.5</v>
       </c>
-      <c r="BU28">
+      <c r="BV28">
         <v>8</v>
       </c>
-      <c r="BV28">
+      <c r="BW28">
         <v>1.999660151270639</v>
       </c>
-      <c r="BW28">
+      <c r="BX28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:75">
+    <row r="29" spans="1:76">
       <c r="A29">
         <v>19</v>
       </c>
@@ -7186,31 +7273,34 @@
         <v>5.8</v>
       </c>
       <c r="BP29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR29">
         <v>0</v>
       </c>
       <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
         <v>40</v>
       </c>
-      <c r="BT29">
+      <c r="BU29">
         <v>2.5</v>
       </c>
-      <c r="BU29">
+      <c r="BV29">
         <v>8</v>
       </c>
-      <c r="BV29">
+      <c r="BW29">
         <v>2.000439292884896</v>
       </c>
-      <c r="BW29">
+      <c r="BX29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:75">
+    <row r="30" spans="1:76">
       <c r="A30">
         <v>30</v>
       </c>
@@ -7413,31 +7503,34 @@
         <v>3.7</v>
       </c>
       <c r="BP30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR30">
         <v>0</v>
       </c>
       <c r="BS30">
+        <v>0</v>
+      </c>
+      <c r="BT30">
         <v>20</v>
       </c>
-      <c r="BT30">
+      <c r="BU30">
         <v>2.5</v>
       </c>
-      <c r="BU30">
+      <c r="BV30">
         <v>10</v>
       </c>
-      <c r="BV30">
+      <c r="BW30">
         <v>1.998779842933656</v>
       </c>
-      <c r="BW30">
+      <c r="BX30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:75">
+    <row r="31" spans="1:76">
       <c r="A31">
         <v>18</v>
       </c>
@@ -7640,27 +7733,30 @@
         <v>3.7</v>
       </c>
       <c r="BP31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR31">
         <v>0</v>
       </c>
       <c r="BS31">
+        <v>0</v>
+      </c>
+      <c r="BT31">
         <v>40</v>
       </c>
-      <c r="BT31">
+      <c r="BU31">
         <v>2.5</v>
       </c>
-      <c r="BU31">
+      <c r="BV31">
         <v>10</v>
       </c>
-      <c r="BV31">
+      <c r="BW31">
         <v>2.000604277156577</v>
       </c>
-      <c r="BW31">
+      <c r="BX31">
         <v>2</v>
       </c>
     </row>
@@ -7671,10 +7767,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BW5"/>
+  <dimension ref="A1:BX5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:75">
+    <row r="1" spans="1:76">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7900,8 +7996,11 @@
       <c r="BW1" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="2" spans="1:75">
+    <row r="2" spans="1:76">
       <c r="A2">
         <v>7</v>
       </c>
@@ -8104,31 +8203,34 @@
         <v>3.1</v>
       </c>
       <c r="BP2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BQ2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BR2">
         <v>-5</v>
       </c>
       <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
         <v>40</v>
       </c>
-      <c r="BT2">
+      <c r="BU2">
         <v>2.5</v>
       </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
       <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
         <v>1.999703047959963</v>
       </c>
-      <c r="BW2">
+      <c r="BX2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:75">
+    <row r="3" spans="1:76">
       <c r="A3">
         <v>8</v>
       </c>
@@ -8331,31 +8433,34 @@
         <v>1.6</v>
       </c>
       <c r="BP3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BQ3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BR3">
         <v>-5</v>
       </c>
       <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
         <v>40</v>
       </c>
-      <c r="BT3">
+      <c r="BU3">
         <v>2.5</v>
       </c>
-      <c r="BU3">
+      <c r="BV3">
         <v>4</v>
       </c>
-      <c r="BV3">
+      <c r="BW3">
         <v>1.99885769582033</v>
       </c>
-      <c r="BW3">
+      <c r="BX3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:75">
+    <row r="4" spans="1:76">
       <c r="A4">
         <v>5</v>
       </c>
@@ -8558,31 +8663,34 @@
         <v>5.8</v>
       </c>
       <c r="BP4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BQ4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BR4">
         <v>-5</v>
       </c>
       <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
         <v>40</v>
       </c>
-      <c r="BT4">
+      <c r="BU4">
         <v>2.5</v>
       </c>
-      <c r="BU4">
+      <c r="BV4">
         <v>8</v>
       </c>
-      <c r="BV4">
+      <c r="BW4">
         <v>1.999309457277746</v>
       </c>
-      <c r="BW4">
+      <c r="BX4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:75">
+    <row r="5" spans="1:76">
       <c r="A5">
         <v>6</v>
       </c>
@@ -8785,27 +8893,30 @@
         <v>3.7</v>
       </c>
       <c r="BP5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BQ5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BR5">
         <v>-5</v>
       </c>
       <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
         <v>40</v>
       </c>
-      <c r="BT5">
+      <c r="BU5">
         <v>2.5</v>
       </c>
-      <c r="BU5">
+      <c r="BV5">
         <v>10</v>
       </c>
-      <c r="BV5">
+      <c r="BW5">
         <v>1.998833184094022</v>
       </c>
-      <c r="BW5">
+      <c r="BX5">
         <v>2</v>
       </c>
     </row>
@@ -8816,10 +8927,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BW18"/>
+  <dimension ref="A1:BX18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:75">
+    <row r="1" spans="1:76">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9045,8 +9156,11 @@
       <c r="BW1" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="2" spans="1:75">
+    <row r="2" spans="1:76">
       <c r="A2">
         <v>1</v>
       </c>
@@ -9249,31 +9363,34 @@
         <v>-6.2</v>
       </c>
       <c r="BP2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR2">
         <v>-10</v>
       </c>
       <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
         <v>40</v>
       </c>
-      <c r="BT2">
+      <c r="BU2">
         <v>-5</v>
       </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
       <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
         <v>1.60036313730308</v>
       </c>
-      <c r="BW2">
+      <c r="BX2">
         <v>1.6</v>
       </c>
     </row>
-    <row r="3" spans="1:75">
+    <row r="3" spans="1:76">
       <c r="A3">
         <v>8</v>
       </c>
@@ -9476,31 +9593,34 @@
         <v>-6.2</v>
       </c>
       <c r="BP3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR3">
         <v>-10</v>
       </c>
       <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
         <v>40</v>
       </c>
-      <c r="BT3">
+      <c r="BU3">
         <v>-5</v>
       </c>
-      <c r="BU3">
-        <v>0</v>
-      </c>
       <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
         <v>2.39953707351704</v>
       </c>
-      <c r="BW3">
+      <c r="BX3">
         <v>2.4</v>
       </c>
     </row>
-    <row r="4" spans="1:75">
+    <row r="4" spans="1:76">
       <c r="A4">
         <v>14</v>
       </c>
@@ -9703,31 +9823,34 @@
         <v>3.1</v>
       </c>
       <c r="BP4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR4">
         <v>-10</v>
       </c>
       <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
         <v>20</v>
       </c>
-      <c r="BT4">
+      <c r="BU4">
         <v>2.5</v>
       </c>
-      <c r="BU4">
-        <v>0</v>
-      </c>
       <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
         <v>1.999944180859678</v>
       </c>
-      <c r="BW4">
+      <c r="BX4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:75">
+    <row r="5" spans="1:76">
       <c r="A5">
         <v>2</v>
       </c>
@@ -9930,31 +10053,34 @@
         <v>3.1</v>
       </c>
       <c r="BP5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR5">
         <v>-10</v>
       </c>
       <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
         <v>40</v>
       </c>
-      <c r="BT5">
+      <c r="BU5">
         <v>2.5</v>
       </c>
-      <c r="BU5">
-        <v>0</v>
-      </c>
       <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
         <v>1.599578178131282</v>
       </c>
-      <c r="BW5">
+      <c r="BX5">
         <v>1.6</v>
       </c>
     </row>
-    <row r="6" spans="1:75">
+    <row r="6" spans="1:76">
       <c r="A6">
         <v>6</v>
       </c>
@@ -10157,31 +10283,34 @@
         <v>3.1</v>
       </c>
       <c r="BP6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR6">
         <v>-10</v>
       </c>
       <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
         <v>40</v>
       </c>
-      <c r="BT6">
+      <c r="BU6">
         <v>2.5</v>
       </c>
-      <c r="BU6">
-        <v>0</v>
-      </c>
       <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
         <v>2.398965083082591</v>
       </c>
-      <c r="BW6">
+      <c r="BX6">
         <v>2.4</v>
       </c>
     </row>
-    <row r="7" spans="1:75">
+    <row r="7" spans="1:76">
       <c r="A7">
         <v>9</v>
       </c>
@@ -10384,31 +10513,34 @@
         <v>3.1</v>
       </c>
       <c r="BP7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR7">
         <v>-10</v>
       </c>
       <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
         <v>40</v>
       </c>
-      <c r="BT7">
+      <c r="BU7">
         <v>2.5</v>
       </c>
-      <c r="BU7">
-        <v>0</v>
-      </c>
       <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
         <v>2.799090928857431</v>
       </c>
-      <c r="BW7">
+      <c r="BX7">
         <v>2.8</v>
       </c>
     </row>
-    <row r="8" spans="1:75">
+    <row r="8" spans="1:76">
       <c r="A8">
         <v>10</v>
       </c>
@@ -10611,31 +10743,34 @@
         <v>3.1</v>
       </c>
       <c r="BP8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR8">
         <v>-10</v>
       </c>
       <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
         <v>40</v>
       </c>
-      <c r="BT8">
+      <c r="BU8">
         <v>2.5</v>
       </c>
-      <c r="BU8">
-        <v>0</v>
-      </c>
       <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
         <v>1.999338931008233</v>
       </c>
-      <c r="BW8">
+      <c r="BX8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:75">
+    <row r="9" spans="1:76">
       <c r="A9">
         <v>3</v>
       </c>
@@ -10838,31 +10973,34 @@
         <v>9.4</v>
       </c>
       <c r="BP9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR9">
         <v>-10</v>
       </c>
       <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
         <v>40</v>
       </c>
-      <c r="BT9">
+      <c r="BU9">
         <v>5</v>
       </c>
-      <c r="BU9">
-        <v>0</v>
-      </c>
       <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
         <v>1.599146051073336</v>
       </c>
-      <c r="BW9">
+      <c r="BX9">
         <v>1.6</v>
       </c>
     </row>
-    <row r="10" spans="1:75">
+    <row r="10" spans="1:76">
       <c r="A10">
         <v>7</v>
       </c>
@@ -11065,31 +11203,34 @@
         <v>9.4</v>
       </c>
       <c r="BP10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR10">
         <v>-10</v>
       </c>
       <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
         <v>40</v>
       </c>
-      <c r="BT10">
+      <c r="BU10">
         <v>5</v>
       </c>
-      <c r="BU10">
-        <v>0</v>
-      </c>
       <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
         <v>2.400613964971563</v>
       </c>
-      <c r="BW10">
+      <c r="BX10">
         <v>2.4</v>
       </c>
     </row>
-    <row r="11" spans="1:75">
+    <row r="11" spans="1:76">
       <c r="A11">
         <v>4</v>
       </c>
@@ -11292,31 +11433,34 @@
         <v>13.75</v>
       </c>
       <c r="BP11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR11">
         <v>-10</v>
       </c>
       <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
         <v>40</v>
       </c>
-      <c r="BT11">
+      <c r="BU11">
         <v>7</v>
       </c>
-      <c r="BU11">
-        <v>0</v>
-      </c>
       <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
         <v>1.599963775959651</v>
       </c>
-      <c r="BW11">
+      <c r="BX11">
         <v>1.6</v>
       </c>
     </row>
-    <row r="12" spans="1:75">
+    <row r="12" spans="1:76">
       <c r="A12">
         <v>5</v>
       </c>
@@ -11519,31 +11663,34 @@
         <v>13.75</v>
       </c>
       <c r="BP12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR12">
         <v>-10</v>
       </c>
       <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
         <v>40</v>
       </c>
-      <c r="BT12">
+      <c r="BU12">
         <v>7</v>
       </c>
-      <c r="BU12">
-        <v>0</v>
-      </c>
       <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
         <v>2.399618044565907</v>
       </c>
-      <c r="BW12">
+      <c r="BX12">
         <v>2.4</v>
       </c>
     </row>
-    <row r="13" spans="1:75">
+    <row r="13" spans="1:76">
       <c r="A13">
         <v>16</v>
       </c>
@@ -11746,31 +11893,34 @@
         <v>1.6</v>
       </c>
       <c r="BP13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR13">
         <v>-10</v>
       </c>
       <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
         <v>20</v>
       </c>
-      <c r="BT13">
+      <c r="BU13">
         <v>2.5</v>
       </c>
-      <c r="BU13">
+      <c r="BV13">
         <v>4</v>
       </c>
-      <c r="BV13">
+      <c r="BW13">
         <v>2.002258777162433</v>
       </c>
-      <c r="BW13">
+      <c r="BX13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:75">
+    <row r="14" spans="1:76">
       <c r="A14">
         <v>11</v>
       </c>
@@ -11973,31 +12123,34 @@
         <v>1.6</v>
       </c>
       <c r="BP14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR14">
         <v>-10</v>
       </c>
       <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
         <v>40</v>
       </c>
-      <c r="BT14">
+      <c r="BU14">
         <v>2.5</v>
       </c>
-      <c r="BU14">
+      <c r="BV14">
         <v>4</v>
       </c>
-      <c r="BV14">
+      <c r="BW14">
         <v>1.999353547798635</v>
       </c>
-      <c r="BW14">
+      <c r="BX14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:75">
+    <row r="15" spans="1:76">
       <c r="A15">
         <v>15</v>
       </c>
@@ -12200,31 +12353,34 @@
         <v>5.8</v>
       </c>
       <c r="BP15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR15">
         <v>-10</v>
       </c>
       <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
         <v>20</v>
       </c>
-      <c r="BT15">
+      <c r="BU15">
         <v>2.5</v>
       </c>
-      <c r="BU15">
+      <c r="BV15">
         <v>8</v>
       </c>
-      <c r="BV15">
+      <c r="BW15">
         <v>1.998725052009657</v>
       </c>
-      <c r="BW15">
+      <c r="BX15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:75">
+    <row r="16" spans="1:76">
       <c r="A16">
         <v>12</v>
       </c>
@@ -12427,31 +12583,34 @@
         <v>5.8</v>
       </c>
       <c r="BP16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR16">
         <v>-10</v>
       </c>
       <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
         <v>40</v>
       </c>
-      <c r="BT16">
+      <c r="BU16">
         <v>2.5</v>
       </c>
-      <c r="BU16">
+      <c r="BV16">
         <v>8</v>
       </c>
-      <c r="BV16">
+      <c r="BW16">
         <v>2.000409905888974</v>
       </c>
-      <c r="BW16">
+      <c r="BX16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:75">
+    <row r="17" spans="1:76">
       <c r="A17">
         <v>17</v>
       </c>
@@ -12654,31 +12813,34 @@
         <v>3.7</v>
       </c>
       <c r="BP17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR17">
         <v>-10</v>
       </c>
       <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
         <v>20</v>
       </c>
-      <c r="BT17">
+      <c r="BU17">
         <v>2.5</v>
       </c>
-      <c r="BU17">
+      <c r="BV17">
         <v>10</v>
       </c>
-      <c r="BV17">
+      <c r="BW17">
         <v>1.99911570666135</v>
       </c>
-      <c r="BW17">
+      <c r="BX17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:75">
+    <row r="18" spans="1:76">
       <c r="A18">
         <v>13</v>
       </c>
@@ -12881,27 +13043,30 @@
         <v>3.7</v>
       </c>
       <c r="BP18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR18">
         <v>-10</v>
       </c>
       <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
         <v>40</v>
       </c>
-      <c r="BT18">
+      <c r="BU18">
         <v>2.5</v>
       </c>
-      <c r="BU18">
+      <c r="BV18">
         <v>10</v>
       </c>
-      <c r="BV18">
+      <c r="BW18">
         <v>1.998996548225215</v>
       </c>
-      <c r="BW18">
+      <c r="BX18">
         <v>2</v>
       </c>
     </row>
@@ -12912,10 +13077,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BW5"/>
+  <dimension ref="A1:BX5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:75">
+    <row r="1" spans="1:76">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13141,8 +13306,11 @@
       <c r="BW1" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="2" spans="1:75">
+    <row r="2" spans="1:76">
       <c r="A2">
         <v>4</v>
       </c>
@@ -13345,31 +13513,34 @@
         <v>3.1</v>
       </c>
       <c r="BP2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BQ2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BR2">
         <v>-20</v>
       </c>
       <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
         <v>40</v>
       </c>
-      <c r="BT2">
+      <c r="BU2">
         <v>2.5</v>
       </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
       <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
         <v>1.999110458881385</v>
       </c>
-      <c r="BW2">
+      <c r="BX2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:75">
+    <row r="3" spans="1:76">
       <c r="A3">
         <v>1</v>
       </c>
@@ -13572,31 +13743,34 @@
         <v>1.6</v>
       </c>
       <c r="BP3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BQ3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BR3">
         <v>-20</v>
       </c>
       <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
         <v>40</v>
       </c>
-      <c r="BT3">
+      <c r="BU3">
         <v>2.5</v>
       </c>
-      <c r="BU3">
+      <c r="BV3">
         <v>4</v>
       </c>
-      <c r="BV3">
+      <c r="BW3">
         <v>1.999530897171809</v>
       </c>
-      <c r="BW3">
+      <c r="BX3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:75">
+    <row r="4" spans="1:76">
       <c r="A4">
         <v>2</v>
       </c>
@@ -13799,31 +13973,34 @@
         <v>5.8</v>
       </c>
       <c r="BP4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BQ4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BR4">
         <v>-20</v>
       </c>
       <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
         <v>40</v>
       </c>
-      <c r="BT4">
+      <c r="BU4">
         <v>2.5</v>
       </c>
-      <c r="BU4">
+      <c r="BV4">
         <v>8</v>
       </c>
-      <c r="BV4">
+      <c r="BW4">
         <v>1.999478033045323</v>
       </c>
-      <c r="BW4">
+      <c r="BX4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:75">
+    <row r="5" spans="1:76">
       <c r="A5">
         <v>3</v>
       </c>
@@ -14026,27 +14203,30 @@
         <v>3.7</v>
       </c>
       <c r="BP5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BQ5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BR5">
         <v>-20</v>
       </c>
       <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
         <v>40</v>
       </c>
-      <c r="BT5">
+      <c r="BU5">
         <v>2.5</v>
       </c>
-      <c r="BU5">
+      <c r="BV5">
         <v>10</v>
       </c>
-      <c r="BV5">
+      <c r="BW5">
         <v>1.999121296346392</v>
       </c>
-      <c r="BW5">
+      <c r="BX5">
         <v>2</v>
       </c>
     </row>
@@ -14057,10 +14237,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BW56"/>
+  <dimension ref="A1:BX56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:75">
+    <row r="1" spans="1:76">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14286,8 +14466,11 @@
       <c r="BW1" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="2" spans="1:75">
+    <row r="2" spans="1:76">
       <c r="A2">
         <v>4</v>
       </c>
@@ -14490,31 +14673,34 @@
         <v>3.1</v>
       </c>
       <c r="BP2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BQ2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BR2">
         <v>-20</v>
       </c>
       <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
         <v>40</v>
       </c>
-      <c r="BT2">
+      <c r="BU2">
         <v>2.5</v>
       </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
       <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
         <v>1.999110458881385</v>
       </c>
-      <c r="BW2">
+      <c r="BX2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:75">
+    <row r="3" spans="1:76">
       <c r="A3">
         <v>1</v>
       </c>
@@ -14717,31 +14903,34 @@
         <v>1.6</v>
       </c>
       <c r="BP3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BQ3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BR3">
         <v>-20</v>
       </c>
       <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
         <v>40</v>
       </c>
-      <c r="BT3">
+      <c r="BU3">
         <v>2.5</v>
       </c>
-      <c r="BU3">
+      <c r="BV3">
         <v>4</v>
       </c>
-      <c r="BV3">
+      <c r="BW3">
         <v>1.999530897171809</v>
       </c>
-      <c r="BW3">
+      <c r="BX3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:75">
+    <row r="4" spans="1:76">
       <c r="A4">
         <v>2</v>
       </c>
@@ -14944,31 +15133,34 @@
         <v>5.8</v>
       </c>
       <c r="BP4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BQ4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BR4">
         <v>-20</v>
       </c>
       <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
         <v>40</v>
       </c>
-      <c r="BT4">
+      <c r="BU4">
         <v>2.5</v>
       </c>
-      <c r="BU4">
+      <c r="BV4">
         <v>8</v>
       </c>
-      <c r="BV4">
+      <c r="BW4">
         <v>1.999478033045323</v>
       </c>
-      <c r="BW4">
+      <c r="BX4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:75">
+    <row r="5" spans="1:76">
       <c r="A5">
         <v>3</v>
       </c>
@@ -15171,31 +15363,34 @@
         <v>3.7</v>
       </c>
       <c r="BP5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BQ5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BR5">
         <v>-20</v>
       </c>
       <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
         <v>40</v>
       </c>
-      <c r="BT5">
+      <c r="BU5">
         <v>2.5</v>
       </c>
-      <c r="BU5">
+      <c r="BV5">
         <v>10</v>
       </c>
-      <c r="BV5">
+      <c r="BW5">
         <v>1.999121296346392</v>
       </c>
-      <c r="BW5">
+      <c r="BX5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:75">
+    <row r="6" spans="1:76">
       <c r="A6">
         <v>1</v>
       </c>
@@ -15398,31 +15593,34 @@
         <v>-6.2</v>
       </c>
       <c r="BP6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR6">
         <v>-10</v>
       </c>
       <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
         <v>40</v>
       </c>
-      <c r="BT6">
+      <c r="BU6">
         <v>-5</v>
       </c>
-      <c r="BU6">
-        <v>0</v>
-      </c>
       <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
         <v>1.60036313730308</v>
       </c>
-      <c r="BW6">
+      <c r="BX6">
         <v>1.6</v>
       </c>
     </row>
-    <row r="7" spans="1:75">
+    <row r="7" spans="1:76">
       <c r="A7">
         <v>8</v>
       </c>
@@ -15625,31 +15823,34 @@
         <v>-6.2</v>
       </c>
       <c r="BP7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR7">
         <v>-10</v>
       </c>
       <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
         <v>40</v>
       </c>
-      <c r="BT7">
+      <c r="BU7">
         <v>-5</v>
       </c>
-      <c r="BU7">
-        <v>0</v>
-      </c>
       <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
         <v>2.39953707351704</v>
       </c>
-      <c r="BW7">
+      <c r="BX7">
         <v>2.4</v>
       </c>
     </row>
-    <row r="8" spans="1:75">
+    <row r="8" spans="1:76">
       <c r="A8">
         <v>14</v>
       </c>
@@ -15852,31 +16053,34 @@
         <v>3.1</v>
       </c>
       <c r="BP8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR8">
         <v>-10</v>
       </c>
       <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
         <v>20</v>
       </c>
-      <c r="BT8">
+      <c r="BU8">
         <v>2.5</v>
       </c>
-      <c r="BU8">
-        <v>0</v>
-      </c>
       <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
         <v>1.999944180859678</v>
       </c>
-      <c r="BW8">
+      <c r="BX8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:75">
+    <row r="9" spans="1:76">
       <c r="A9">
         <v>2</v>
       </c>
@@ -16079,31 +16283,34 @@
         <v>3.1</v>
       </c>
       <c r="BP9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR9">
         <v>-10</v>
       </c>
       <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
         <v>40</v>
       </c>
-      <c r="BT9">
+      <c r="BU9">
         <v>2.5</v>
       </c>
-      <c r="BU9">
-        <v>0</v>
-      </c>
       <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
         <v>1.599578178131282</v>
       </c>
-      <c r="BW9">
+      <c r="BX9">
         <v>1.6</v>
       </c>
     </row>
-    <row r="10" spans="1:75">
+    <row r="10" spans="1:76">
       <c r="A10">
         <v>6</v>
       </c>
@@ -16306,31 +16513,34 @@
         <v>3.1</v>
       </c>
       <c r="BP10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR10">
         <v>-10</v>
       </c>
       <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
         <v>40</v>
       </c>
-      <c r="BT10">
+      <c r="BU10">
         <v>2.5</v>
       </c>
-      <c r="BU10">
-        <v>0</v>
-      </c>
       <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
         <v>2.398965083082591</v>
       </c>
-      <c r="BW10">
+      <c r="BX10">
         <v>2.4</v>
       </c>
     </row>
-    <row r="11" spans="1:75">
+    <row r="11" spans="1:76">
       <c r="A11">
         <v>9</v>
       </c>
@@ -16533,31 +16743,34 @@
         <v>3.1</v>
       </c>
       <c r="BP11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR11">
         <v>-10</v>
       </c>
       <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
         <v>40</v>
       </c>
-      <c r="BT11">
+      <c r="BU11">
         <v>2.5</v>
       </c>
-      <c r="BU11">
-        <v>0</v>
-      </c>
       <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
         <v>2.799090928857431</v>
       </c>
-      <c r="BW11">
+      <c r="BX11">
         <v>2.8</v>
       </c>
     </row>
-    <row r="12" spans="1:75">
+    <row r="12" spans="1:76">
       <c r="A12">
         <v>10</v>
       </c>
@@ -16760,31 +16973,34 @@
         <v>3.1</v>
       </c>
       <c r="BP12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR12">
         <v>-10</v>
       </c>
       <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
         <v>40</v>
       </c>
-      <c r="BT12">
+      <c r="BU12">
         <v>2.5</v>
       </c>
-      <c r="BU12">
-        <v>0</v>
-      </c>
       <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
         <v>1.999338931008233</v>
       </c>
-      <c r="BW12">
+      <c r="BX12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:75">
+    <row r="13" spans="1:76">
       <c r="A13">
         <v>3</v>
       </c>
@@ -16987,31 +17203,34 @@
         <v>9.4</v>
       </c>
       <c r="BP13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR13">
         <v>-10</v>
       </c>
       <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
         <v>40</v>
       </c>
-      <c r="BT13">
+      <c r="BU13">
         <v>5</v>
       </c>
-      <c r="BU13">
-        <v>0</v>
-      </c>
       <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
         <v>1.599146051073336</v>
       </c>
-      <c r="BW13">
+      <c r="BX13">
         <v>1.6</v>
       </c>
     </row>
-    <row r="14" spans="1:75">
+    <row r="14" spans="1:76">
       <c r="A14">
         <v>7</v>
       </c>
@@ -17214,31 +17433,34 @@
         <v>9.4</v>
       </c>
       <c r="BP14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR14">
         <v>-10</v>
       </c>
       <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
         <v>40</v>
       </c>
-      <c r="BT14">
+      <c r="BU14">
         <v>5</v>
       </c>
-      <c r="BU14">
-        <v>0</v>
-      </c>
       <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
         <v>2.400613964971563</v>
       </c>
-      <c r="BW14">
+      <c r="BX14">
         <v>2.4</v>
       </c>
     </row>
-    <row r="15" spans="1:75">
+    <row r="15" spans="1:76">
       <c r="A15">
         <v>4</v>
       </c>
@@ -17441,31 +17663,34 @@
         <v>13.75</v>
       </c>
       <c r="BP15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR15">
         <v>-10</v>
       </c>
       <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
         <v>40</v>
       </c>
-      <c r="BT15">
+      <c r="BU15">
         <v>7</v>
       </c>
-      <c r="BU15">
-        <v>0</v>
-      </c>
       <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
         <v>1.599963775959651</v>
       </c>
-      <c r="BW15">
+      <c r="BX15">
         <v>1.6</v>
       </c>
     </row>
-    <row r="16" spans="1:75">
+    <row r="16" spans="1:76">
       <c r="A16">
         <v>5</v>
       </c>
@@ -17668,31 +17893,34 @@
         <v>13.75</v>
       </c>
       <c r="BP16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR16">
         <v>-10</v>
       </c>
       <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
         <v>40</v>
       </c>
-      <c r="BT16">
+      <c r="BU16">
         <v>7</v>
       </c>
-      <c r="BU16">
-        <v>0</v>
-      </c>
       <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
         <v>2.399618044565907</v>
       </c>
-      <c r="BW16">
+      <c r="BX16">
         <v>2.4</v>
       </c>
     </row>
-    <row r="17" spans="1:75">
+    <row r="17" spans="1:76">
       <c r="A17">
         <v>16</v>
       </c>
@@ -17895,31 +18123,34 @@
         <v>1.6</v>
       </c>
       <c r="BP17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR17">
         <v>-10</v>
       </c>
       <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
         <v>20</v>
       </c>
-      <c r="BT17">
+      <c r="BU17">
         <v>2.5</v>
       </c>
-      <c r="BU17">
+      <c r="BV17">
         <v>4</v>
       </c>
-      <c r="BV17">
+      <c r="BW17">
         <v>2.002258777162433</v>
       </c>
-      <c r="BW17">
+      <c r="BX17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:75">
+    <row r="18" spans="1:76">
       <c r="A18">
         <v>11</v>
       </c>
@@ -18122,31 +18353,34 @@
         <v>1.6</v>
       </c>
       <c r="BP18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR18">
         <v>-10</v>
       </c>
       <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
         <v>40</v>
       </c>
-      <c r="BT18">
+      <c r="BU18">
         <v>2.5</v>
       </c>
-      <c r="BU18">
+      <c r="BV18">
         <v>4</v>
       </c>
-      <c r="BV18">
+      <c r="BW18">
         <v>1.999353547798635</v>
       </c>
-      <c r="BW18">
+      <c r="BX18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:75">
+    <row r="19" spans="1:76">
       <c r="A19">
         <v>15</v>
       </c>
@@ -18349,31 +18583,34 @@
         <v>5.8</v>
       </c>
       <c r="BP19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR19">
         <v>-10</v>
       </c>
       <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
         <v>20</v>
       </c>
-      <c r="BT19">
+      <c r="BU19">
         <v>2.5</v>
       </c>
-      <c r="BU19">
+      <c r="BV19">
         <v>8</v>
       </c>
-      <c r="BV19">
+      <c r="BW19">
         <v>1.998725052009657</v>
       </c>
-      <c r="BW19">
+      <c r="BX19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:75">
+    <row r="20" spans="1:76">
       <c r="A20">
         <v>12</v>
       </c>
@@ -18576,31 +18813,34 @@
         <v>5.8</v>
       </c>
       <c r="BP20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR20">
         <v>-10</v>
       </c>
       <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
         <v>40</v>
       </c>
-      <c r="BT20">
+      <c r="BU20">
         <v>2.5</v>
       </c>
-      <c r="BU20">
+      <c r="BV20">
         <v>8</v>
       </c>
-      <c r="BV20">
+      <c r="BW20">
         <v>2.000409905888974</v>
       </c>
-      <c r="BW20">
+      <c r="BX20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:75">
+    <row r="21" spans="1:76">
       <c r="A21">
         <v>17</v>
       </c>
@@ -18803,31 +19043,34 @@
         <v>3.7</v>
       </c>
       <c r="BP21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR21">
         <v>-10</v>
       </c>
       <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
         <v>20</v>
       </c>
-      <c r="BT21">
+      <c r="BU21">
         <v>2.5</v>
       </c>
-      <c r="BU21">
+      <c r="BV21">
         <v>10</v>
       </c>
-      <c r="BV21">
+      <c r="BW21">
         <v>1.99911570666135</v>
       </c>
-      <c r="BW21">
+      <c r="BX21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:75">
+    <row r="22" spans="1:76">
       <c r="A22">
         <v>13</v>
       </c>
@@ -19030,31 +19273,34 @@
         <v>3.7</v>
       </c>
       <c r="BP22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BQ22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BR22">
         <v>-10</v>
       </c>
       <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
         <v>40</v>
       </c>
-      <c r="BT22">
+      <c r="BU22">
         <v>2.5</v>
       </c>
-      <c r="BU22">
+      <c r="BV22">
         <v>10</v>
       </c>
-      <c r="BV22">
+      <c r="BW22">
         <v>1.998996548225215</v>
       </c>
-      <c r="BW22">
+      <c r="BX22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:75">
+    <row r="23" spans="1:76">
       <c r="A23">
         <v>7</v>
       </c>
@@ -19257,31 +19503,34 @@
         <v>3.1</v>
       </c>
       <c r="BP23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BQ23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BR23">
         <v>-5</v>
       </c>
       <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
         <v>40</v>
       </c>
-      <c r="BT23">
+      <c r="BU23">
         <v>2.5</v>
       </c>
-      <c r="BU23">
-        <v>0</v>
-      </c>
       <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
         <v>1.999703047959963</v>
       </c>
-      <c r="BW23">
+      <c r="BX23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:75">
+    <row r="24" spans="1:76">
       <c r="A24">
         <v>8</v>
       </c>
@@ -19484,31 +19733,34 @@
         <v>1.6</v>
       </c>
       <c r="BP24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BQ24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BR24">
         <v>-5</v>
       </c>
       <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
         <v>40</v>
       </c>
-      <c r="BT24">
+      <c r="BU24">
         <v>2.5</v>
       </c>
-      <c r="BU24">
+      <c r="BV24">
         <v>4</v>
       </c>
-      <c r="BV24">
+      <c r="BW24">
         <v>1.99885769582033</v>
       </c>
-      <c r="BW24">
+      <c r="BX24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:75">
+    <row r="25" spans="1:76">
       <c r="A25">
         <v>5</v>
       </c>
@@ -19711,31 +19963,34 @@
         <v>5.8</v>
       </c>
       <c r="BP25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BQ25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BR25">
         <v>-5</v>
       </c>
       <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
         <v>40</v>
       </c>
-      <c r="BT25">
+      <c r="BU25">
         <v>2.5</v>
       </c>
-      <c r="BU25">
+      <c r="BV25">
         <v>8</v>
       </c>
-      <c r="BV25">
+      <c r="BW25">
         <v>1.999309457277746</v>
       </c>
-      <c r="BW25">
+      <c r="BX25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:75">
+    <row r="26" spans="1:76">
       <c r="A26">
         <v>6</v>
       </c>
@@ -19938,31 +20193,34 @@
         <v>3.7</v>
       </c>
       <c r="BP26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BQ26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BR26">
         <v>-5</v>
       </c>
       <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
         <v>40</v>
       </c>
-      <c r="BT26">
+      <c r="BU26">
         <v>2.5</v>
       </c>
-      <c r="BU26">
+      <c r="BV26">
         <v>10</v>
       </c>
-      <c r="BV26">
+      <c r="BW26">
         <v>1.998833184094022</v>
       </c>
-      <c r="BW26">
+      <c r="BX26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:75">
+    <row r="27" spans="1:76">
       <c r="A27">
         <v>28</v>
       </c>
@@ -20165,31 +20423,34 @@
         <v>-22.5</v>
       </c>
       <c r="BP27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR27">
         <v>0</v>
       </c>
       <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
         <v>20</v>
       </c>
-      <c r="BT27">
+      <c r="BU27">
         <v>2.5</v>
       </c>
-      <c r="BU27">
+      <c r="BV27">
         <v>-10</v>
       </c>
-      <c r="BV27">
+      <c r="BW27">
         <v>1.9981249644582</v>
       </c>
-      <c r="BW27">
+      <c r="BX27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:75">
+    <row r="28" spans="1:76">
       <c r="A28">
         <v>20</v>
       </c>
@@ -20392,31 +20653,34 @@
         <v>-22.5</v>
       </c>
       <c r="BP28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR28">
         <v>0</v>
       </c>
       <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
         <v>40</v>
       </c>
-      <c r="BT28">
+      <c r="BU28">
         <v>2.5</v>
       </c>
-      <c r="BU28">
+      <c r="BV28">
         <v>-10</v>
       </c>
-      <c r="BV28">
+      <c r="BW28">
         <v>1.999624949296554</v>
       </c>
-      <c r="BW28">
+      <c r="BX28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:75">
+    <row r="29" spans="1:76">
       <c r="A29">
         <v>26</v>
       </c>
@@ -20619,31 +20883,34 @@
         <v>-13.9</v>
       </c>
       <c r="BP29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR29">
         <v>0</v>
       </c>
       <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
         <v>20</v>
       </c>
-      <c r="BT29">
+      <c r="BU29">
         <v>2.5</v>
       </c>
-      <c r="BU29">
+      <c r="BV29">
         <v>-8</v>
       </c>
-      <c r="BV29">
+      <c r="BW29">
         <v>1.998061565906423</v>
       </c>
-      <c r="BW29">
+      <c r="BX29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:75">
+    <row r="30" spans="1:76">
       <c r="A30">
         <v>25</v>
       </c>
@@ -20846,31 +21113,34 @@
         <v>-7.8</v>
       </c>
       <c r="BP30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR30">
         <v>0</v>
       </c>
       <c r="BS30">
+        <v>0</v>
+      </c>
+      <c r="BT30">
         <v>20</v>
       </c>
-      <c r="BT30">
+      <c r="BU30">
         <v>2.5</v>
       </c>
-      <c r="BU30">
+      <c r="BV30">
         <v>-4</v>
       </c>
-      <c r="BV30">
+      <c r="BW30">
         <v>1.999052185353145</v>
       </c>
-      <c r="BW30">
+      <c r="BX30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:75">
+    <row r="31" spans="1:76">
       <c r="A31">
         <v>15</v>
       </c>
@@ -21073,31 +21343,34 @@
         <v>-7.8</v>
       </c>
       <c r="BP31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR31">
         <v>0</v>
       </c>
       <c r="BS31">
+        <v>0</v>
+      </c>
+      <c r="BT31">
         <v>40</v>
       </c>
-      <c r="BT31">
+      <c r="BU31">
         <v>2.5</v>
       </c>
-      <c r="BU31">
+      <c r="BV31">
         <v>-4</v>
       </c>
-      <c r="BV31">
+      <c r="BW31">
         <v>1.999134042244398</v>
       </c>
-      <c r="BW31">
+      <c r="BX31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:75">
+    <row r="32" spans="1:76">
       <c r="A32">
         <v>1</v>
       </c>
@@ -21300,31 +21573,34 @@
         <v>-6.2</v>
       </c>
       <c r="BP32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR32">
         <v>0</v>
       </c>
       <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
         <v>40</v>
       </c>
-      <c r="BT32">
+      <c r="BU32">
         <v>-5</v>
       </c>
-      <c r="BU32">
-        <v>0</v>
-      </c>
       <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
         <v>1.599628523547783</v>
       </c>
-      <c r="BW32">
+      <c r="BX32">
         <v>1.6</v>
       </c>
     </row>
-    <row r="33" spans="1:75">
+    <row r="33" spans="1:76">
       <c r="A33">
         <v>7</v>
       </c>
@@ -21527,31 +21803,34 @@
         <v>-6.2</v>
       </c>
       <c r="BP33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR33">
         <v>0</v>
       </c>
       <c r="BS33">
+        <v>0</v>
+      </c>
+      <c r="BT33">
         <v>40</v>
       </c>
-      <c r="BT33">
+      <c r="BU33">
         <v>-5</v>
       </c>
-      <c r="BU33">
-        <v>0</v>
-      </c>
       <c r="BV33">
+        <v>0</v>
+      </c>
+      <c r="BW33">
         <v>2.398452479684511</v>
       </c>
-      <c r="BW33">
+      <c r="BX33">
         <v>2.4</v>
       </c>
     </row>
-    <row r="34" spans="1:75">
+    <row r="34" spans="1:76">
       <c r="A34">
         <v>21</v>
       </c>
@@ -21754,31 +22033,34 @@
         <v>3.1</v>
       </c>
       <c r="BP34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR34">
         <v>0</v>
       </c>
       <c r="BS34">
+        <v>0</v>
+      </c>
+      <c r="BT34">
         <v>20</v>
       </c>
-      <c r="BT34">
+      <c r="BU34">
         <v>2.5</v>
       </c>
-      <c r="BU34">
-        <v>0</v>
-      </c>
       <c r="BV34">
+        <v>0</v>
+      </c>
+      <c r="BW34">
         <v>1.600409102342839</v>
       </c>
-      <c r="BW34">
+      <c r="BX34">
         <v>1.6</v>
       </c>
     </row>
-    <row r="35" spans="1:75">
+    <row r="35" spans="1:76">
       <c r="A35">
         <v>22</v>
       </c>
@@ -21981,31 +22263,34 @@
         <v>3.1</v>
       </c>
       <c r="BP35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR35">
         <v>0</v>
       </c>
       <c r="BS35">
+        <v>0</v>
+      </c>
+      <c r="BT35">
         <v>20</v>
       </c>
-      <c r="BT35">
+      <c r="BU35">
         <v>2.5</v>
       </c>
-      <c r="BU35">
-        <v>0</v>
-      </c>
       <c r="BV35">
+        <v>0</v>
+      </c>
+      <c r="BW35">
         <v>2.40006841422405</v>
       </c>
-      <c r="BW35">
+      <c r="BX35">
         <v>2.4</v>
       </c>
     </row>
-    <row r="36" spans="1:75">
+    <row r="36" spans="1:76">
       <c r="A36">
         <v>23</v>
       </c>
@@ -22208,31 +22493,34 @@
         <v>3.1</v>
       </c>
       <c r="BP36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR36">
         <v>0</v>
       </c>
       <c r="BS36">
+        <v>0</v>
+      </c>
+      <c r="BT36">
         <v>20</v>
       </c>
-      <c r="BT36">
+      <c r="BU36">
         <v>2.5</v>
       </c>
-      <c r="BU36">
-        <v>0</v>
-      </c>
       <c r="BV36">
+        <v>0</v>
+      </c>
+      <c r="BW36">
         <v>2.798598214688046</v>
       </c>
-      <c r="BW36">
+      <c r="BX36">
         <v>2.8</v>
       </c>
     </row>
-    <row r="37" spans="1:75">
+    <row r="37" spans="1:76">
       <c r="A37">
         <v>24</v>
       </c>
@@ -22435,31 +22723,34 @@
         <v>3.1</v>
       </c>
       <c r="BP37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR37">
         <v>0</v>
       </c>
       <c r="BS37">
+        <v>0</v>
+      </c>
+      <c r="BT37">
         <v>20</v>
       </c>
-      <c r="BT37">
+      <c r="BU37">
         <v>2.5</v>
       </c>
-      <c r="BU37">
-        <v>0</v>
-      </c>
       <c r="BV37">
+        <v>0</v>
+      </c>
+      <c r="BW37">
         <v>2.000930815102612</v>
       </c>
-      <c r="BW37">
+      <c r="BX37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:75">
+    <row r="38" spans="1:76">
       <c r="A38">
         <v>4</v>
       </c>
@@ -22662,31 +22953,34 @@
         <v>3.1</v>
       </c>
       <c r="BP38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR38">
         <v>0</v>
       </c>
       <c r="BS38">
+        <v>0</v>
+      </c>
+      <c r="BT38">
         <v>40</v>
       </c>
-      <c r="BT38">
+      <c r="BU38">
         <v>2.5</v>
       </c>
-      <c r="BU38">
-        <v>0</v>
-      </c>
       <c r="BV38">
+        <v>0</v>
+      </c>
+      <c r="BW38">
         <v>1.599716975777331</v>
       </c>
-      <c r="BW38">
+      <c r="BX38">
         <v>1.6</v>
       </c>
     </row>
-    <row r="39" spans="1:75">
+    <row r="39" spans="1:76">
       <c r="A39">
         <v>10</v>
       </c>
@@ -22889,31 +23183,34 @@
         <v>3.1</v>
       </c>
       <c r="BP39" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR39">
         <v>0</v>
       </c>
       <c r="BS39">
+        <v>0</v>
+      </c>
+      <c r="BT39">
         <v>40</v>
       </c>
-      <c r="BT39">
+      <c r="BU39">
         <v>2.5</v>
       </c>
-      <c r="BU39">
-        <v>0</v>
-      </c>
       <c r="BV39">
+        <v>0</v>
+      </c>
+      <c r="BW39">
         <v>2.400019135102187</v>
       </c>
-      <c r="BW39">
+      <c r="BX39">
         <v>2.4</v>
       </c>
     </row>
-    <row r="40" spans="1:75">
+    <row r="40" spans="1:76">
       <c r="A40">
         <v>11</v>
       </c>
@@ -23116,31 +23413,34 @@
         <v>3.1</v>
       </c>
       <c r="BP40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR40">
         <v>0</v>
       </c>
       <c r="BS40">
+        <v>0</v>
+      </c>
+      <c r="BT40">
         <v>40</v>
       </c>
-      <c r="BT40">
+      <c r="BU40">
         <v>2.5</v>
       </c>
-      <c r="BU40">
-        <v>0</v>
-      </c>
       <c r="BV40">
+        <v>0</v>
+      </c>
+      <c r="BW40">
         <v>2.799343737351262</v>
       </c>
-      <c r="BW40">
+      <c r="BX40">
         <v>2.8</v>
       </c>
     </row>
-    <row r="41" spans="1:75">
+    <row r="41" spans="1:76">
       <c r="A41">
         <v>12</v>
       </c>
@@ -23343,31 +23643,34 @@
         <v>3.1</v>
       </c>
       <c r="BP41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ41" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR41">
         <v>0</v>
       </c>
       <c r="BS41">
+        <v>0</v>
+      </c>
+      <c r="BT41">
         <v>40</v>
       </c>
-      <c r="BT41">
+      <c r="BU41">
         <v>2.5</v>
       </c>
-      <c r="BU41">
-        <v>0</v>
-      </c>
       <c r="BV41">
+        <v>0</v>
+      </c>
+      <c r="BW41">
         <v>2.00005296202351</v>
       </c>
-      <c r="BW41">
+      <c r="BX41">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:75">
+    <row r="42" spans="1:76">
       <c r="A42">
         <v>2</v>
       </c>
@@ -23570,31 +23873,34 @@
         <v>9.4</v>
       </c>
       <c r="BP42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR42">
         <v>0</v>
       </c>
       <c r="BS42">
+        <v>0</v>
+      </c>
+      <c r="BT42">
         <v>40</v>
       </c>
-      <c r="BT42">
+      <c r="BU42">
         <v>5</v>
       </c>
-      <c r="BU42">
-        <v>0</v>
-      </c>
       <c r="BV42">
+        <v>0</v>
+      </c>
+      <c r="BW42">
         <v>1.599983067669266</v>
       </c>
-      <c r="BW42">
+      <c r="BX42">
         <v>1.6</v>
       </c>
     </row>
-    <row r="43" spans="1:75">
+    <row r="43" spans="1:76">
       <c r="A43">
         <v>9</v>
       </c>
@@ -23797,31 +24103,34 @@
         <v>9.4</v>
       </c>
       <c r="BP43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ43" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR43">
         <v>0</v>
       </c>
       <c r="BS43">
+        <v>0</v>
+      </c>
+      <c r="BT43">
         <v>40</v>
       </c>
-      <c r="BT43">
+      <c r="BU43">
         <v>5</v>
       </c>
-      <c r="BU43">
-        <v>0</v>
-      </c>
       <c r="BV43">
+        <v>0</v>
+      </c>
+      <c r="BW43">
         <v>2.399774097228049</v>
       </c>
-      <c r="BW43">
+      <c r="BX43">
         <v>2.4</v>
       </c>
     </row>
-    <row r="44" spans="1:75">
+    <row r="44" spans="1:76">
       <c r="A44">
         <v>3</v>
       </c>
@@ -24024,31 +24333,34 @@
         <v>13.75</v>
       </c>
       <c r="BP44" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ44" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR44">
         <v>0</v>
       </c>
       <c r="BS44">
+        <v>0</v>
+      </c>
+      <c r="BT44">
         <v>40</v>
       </c>
-      <c r="BT44">
+      <c r="BU44">
         <v>7</v>
       </c>
-      <c r="BU44">
-        <v>0</v>
-      </c>
       <c r="BV44">
+        <v>0</v>
+      </c>
+      <c r="BW44">
         <v>1.599296490435402</v>
       </c>
-      <c r="BW44">
+      <c r="BX44">
         <v>1.6</v>
       </c>
     </row>
-    <row r="45" spans="1:75">
+    <row r="45" spans="1:76">
       <c r="A45">
         <v>6</v>
       </c>
@@ -24251,31 +24563,34 @@
         <v>13.75</v>
       </c>
       <c r="BP45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ45" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR45">
         <v>0</v>
       </c>
       <c r="BS45">
+        <v>0</v>
+      </c>
+      <c r="BT45">
         <v>40</v>
       </c>
-      <c r="BT45">
+      <c r="BU45">
         <v>7</v>
       </c>
-      <c r="BU45">
-        <v>0</v>
-      </c>
       <c r="BV45">
+        <v>0</v>
+      </c>
+      <c r="BW45">
         <v>2.400793968982889</v>
       </c>
-      <c r="BW45">
+      <c r="BX45">
         <v>2.4</v>
       </c>
     </row>
-    <row r="46" spans="1:75">
+    <row r="46" spans="1:76">
       <c r="A46">
         <v>5</v>
       </c>
@@ -24478,31 +24793,34 @@
         <v>11.5</v>
       </c>
       <c r="BP46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ46" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR46">
         <v>0</v>
       </c>
       <c r="BS46">
+        <v>0</v>
+      </c>
+      <c r="BT46">
         <v>40</v>
       </c>
-      <c r="BT46">
+      <c r="BU46">
         <v>8</v>
       </c>
-      <c r="BU46">
-        <v>0</v>
-      </c>
       <c r="BV46">
+        <v>0</v>
+      </c>
+      <c r="BW46">
         <v>1.59988495034755</v>
       </c>
-      <c r="BW46">
+      <c r="BX46">
         <v>1.6</v>
       </c>
     </row>
-    <row r="47" spans="1:75">
+    <row r="47" spans="1:76">
       <c r="A47">
         <v>8</v>
       </c>
@@ -24705,31 +25023,34 @@
         <v>11.5</v>
       </c>
       <c r="BP47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR47">
         <v>0</v>
       </c>
       <c r="BS47">
+        <v>0</v>
+      </c>
+      <c r="BT47">
         <v>40</v>
       </c>
-      <c r="BT47">
+      <c r="BU47">
         <v>8</v>
       </c>
-      <c r="BU47">
-        <v>0</v>
-      </c>
       <c r="BV47">
+        <v>0</v>
+      </c>
+      <c r="BW47">
         <v>2.400401445800175</v>
       </c>
-      <c r="BW47">
+      <c r="BX47">
         <v>2.4</v>
       </c>
     </row>
-    <row r="48" spans="1:75">
+    <row r="48" spans="1:76">
       <c r="A48">
         <v>13</v>
       </c>
@@ -24932,31 +25253,34 @@
         <v>11.5</v>
       </c>
       <c r="BP48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR48">
         <v>0</v>
       </c>
       <c r="BS48">
+        <v>0</v>
+      </c>
+      <c r="BT48">
         <v>40</v>
       </c>
-      <c r="BT48">
+      <c r="BU48">
         <v>8</v>
       </c>
-      <c r="BU48">
-        <v>0</v>
-      </c>
       <c r="BV48">
+        <v>0</v>
+      </c>
+      <c r="BW48">
         <v>1.999514789764307</v>
       </c>
-      <c r="BW48">
+      <c r="BX48">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:75">
+    <row r="49" spans="1:76">
       <c r="A49">
         <v>27</v>
       </c>
@@ -25159,31 +25483,34 @@
         <v>1.6</v>
       </c>
       <c r="BP49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR49">
         <v>0</v>
       </c>
       <c r="BS49">
+        <v>0</v>
+      </c>
+      <c r="BT49">
         <v>20</v>
       </c>
-      <c r="BT49">
+      <c r="BU49">
         <v>2.5</v>
       </c>
-      <c r="BU49">
+      <c r="BV49">
         <v>4</v>
       </c>
-      <c r="BV49">
+      <c r="BW49">
         <v>2.00257726863807</v>
       </c>
-      <c r="BW49">
+      <c r="BX49">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:75">
+    <row r="50" spans="1:76">
       <c r="A50">
         <v>16</v>
       </c>
@@ -25386,31 +25713,34 @@
         <v>1.6</v>
       </c>
       <c r="BP50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR50">
         <v>0</v>
       </c>
       <c r="BS50">
+        <v>0</v>
+      </c>
+      <c r="BT50">
         <v>40</v>
       </c>
-      <c r="BT50">
+      <c r="BU50">
         <v>2.5</v>
       </c>
-      <c r="BU50">
+      <c r="BV50">
         <v>4</v>
       </c>
-      <c r="BV50">
+      <c r="BW50">
         <v>1.996844465052762</v>
       </c>
-      <c r="BW50">
+      <c r="BX50">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:75">
+    <row r="51" spans="1:76">
       <c r="A51">
         <v>17</v>
       </c>
@@ -25613,31 +25943,34 @@
         <v>1.6</v>
       </c>
       <c r="BP51" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR51">
         <v>0</v>
       </c>
       <c r="BS51">
+        <v>0</v>
+      </c>
+      <c r="BT51">
         <v>40</v>
       </c>
-      <c r="BT51">
+      <c r="BU51">
         <v>2.5</v>
       </c>
-      <c r="BU51">
+      <c r="BV51">
         <v>4</v>
       </c>
-      <c r="BV51">
+      <c r="BW51">
         <v>1.999311380750595</v>
       </c>
-      <c r="BW51">
+      <c r="BX51">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:75">
+    <row r="52" spans="1:76">
       <c r="A52">
         <v>29</v>
       </c>
@@ -25840,31 +26173,34 @@
         <v>5.8</v>
       </c>
       <c r="BP52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR52">
         <v>0</v>
       </c>
       <c r="BS52">
+        <v>0</v>
+      </c>
+      <c r="BT52">
         <v>20</v>
       </c>
-      <c r="BT52">
+      <c r="BU52">
         <v>2.5</v>
       </c>
-      <c r="BU52">
+      <c r="BV52">
         <v>8</v>
       </c>
-      <c r="BV52">
+      <c r="BW52">
         <v>2.000608505594573</v>
       </c>
-      <c r="BW52">
+      <c r="BX52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:75">
+    <row r="53" spans="1:76">
       <c r="A53">
         <v>14</v>
       </c>
@@ -26067,31 +26403,34 @@
         <v>5.8</v>
       </c>
       <c r="BP53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR53">
         <v>0</v>
       </c>
       <c r="BS53">
+        <v>0</v>
+      </c>
+      <c r="BT53">
         <v>40</v>
       </c>
-      <c r="BT53">
+      <c r="BU53">
         <v>2.5</v>
       </c>
-      <c r="BU53">
+      <c r="BV53">
         <v>8</v>
       </c>
-      <c r="BV53">
+      <c r="BW53">
         <v>1.999660151270639</v>
       </c>
-      <c r="BW53">
+      <c r="BX53">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:75">
+    <row r="54" spans="1:76">
       <c r="A54">
         <v>19</v>
       </c>
@@ -26294,31 +26633,34 @@
         <v>5.8</v>
       </c>
       <c r="BP54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR54">
         <v>0</v>
       </c>
       <c r="BS54">
+        <v>0</v>
+      </c>
+      <c r="BT54">
         <v>40</v>
       </c>
-      <c r="BT54">
+      <c r="BU54">
         <v>2.5</v>
       </c>
-      <c r="BU54">
+      <c r="BV54">
         <v>8</v>
       </c>
-      <c r="BV54">
+      <c r="BW54">
         <v>2.000439292884896</v>
       </c>
-      <c r="BW54">
+      <c r="BX54">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:75">
+    <row r="55" spans="1:76">
       <c r="A55">
         <v>30</v>
       </c>
@@ -26521,31 +26863,34 @@
         <v>3.7</v>
       </c>
       <c r="BP55" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ55" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR55">
         <v>0</v>
       </c>
       <c r="BS55">
+        <v>0</v>
+      </c>
+      <c r="BT55">
         <v>20</v>
       </c>
-      <c r="BT55">
+      <c r="BU55">
         <v>2.5</v>
       </c>
-      <c r="BU55">
+      <c r="BV55">
         <v>10</v>
       </c>
-      <c r="BV55">
+      <c r="BW55">
         <v>1.998779842933656</v>
       </c>
-      <c r="BW55">
+      <c r="BX55">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:75">
+    <row r="56" spans="1:76">
       <c r="A56">
         <v>18</v>
       </c>
@@ -26748,27 +27093,30 @@
         <v>3.7</v>
       </c>
       <c r="BP56" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BQ56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BR56">
         <v>0</v>
       </c>
       <c r="BS56">
+        <v>0</v>
+      </c>
+      <c r="BT56">
         <v>40</v>
       </c>
-      <c r="BT56">
+      <c r="BU56">
         <v>2.5</v>
       </c>
-      <c r="BU56">
+      <c r="BV56">
         <v>10</v>
       </c>
-      <c r="BV56">
+      <c r="BW56">
         <v>2.000604277156577</v>
       </c>
-      <c r="BW56">
+      <c r="BX56">
         <v>2</v>
       </c>
     </row>
